--- a/www/download/COUNTRY.USA.rpA1.xlsx
+++ b/www/download/COUNTRY.USA.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.0000000020846</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>0.999999998842423</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.999999995079282</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>0.99999999562278</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>0.999999996660455</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1.00000000300325</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>0.9999999982869</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>0.999999996719295</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>0.999999999213553</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.00000000130348</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.000000002288</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.999999996442966</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>1.00000000279833</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>1.00000000415777</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.308</t>
+          <t>0.999999995453474</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>133.979</t>
+          <t>0.198336693127675</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>136.023</t>
+          <t>0.22641951990651</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>138.548</t>
+          <t>0.210655445746357</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>141.887</t>
+          <t>0.144930835761122</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>144.534</t>
+          <t>0.119104432990576</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>147.717</t>
+          <t>-0.0195559142135252</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>146.818</t>
+          <t>-0.0636201630721139</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>145.399</t>
+          <t>-0.0830960461801383</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>145.189</t>
+          <t>-0.11289798726459</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>146.865</t>
+          <t>-0.139127177556245</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>148.903</t>
+          <t>-0.139262760829738</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>151.319</t>
+          <t>-0.122463645427489</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>152.567</t>
+          <t>-0.0318033765025414</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>151.743</t>
+          <t>0.0312577072332438</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>145.345</t>
+          <t>0.0514857657437795</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>123.518</t>
+          <t>0.981252681083073</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>125.56</t>
+          <t>1.02713743848267</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128.056</t>
+          <t>1.05302030640968</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>131.603</t>
+          <t>0.957494193123214</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>134.466</t>
+          <t>0.892648805777819</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>137.538</t>
+          <t>0.766124946523622</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136.742</t>
+          <t>0.700399481893014</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>135.486</t>
+          <t>0.641255425431836</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>134.951</t>
+          <t>0.593041153658132</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>136.496</t>
+          <t>0.589715782207848</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>139.146</t>
+          <t>0.584127434294385</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>141.466</t>
+          <t>0.649603208018224</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>142.838</t>
+          <t>0.756984514499002</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>142.317</t>
+          <t>0.887103476889034</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>136.175</t>
+          <t>0.943916173478742</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>242776.093</t>
+          <t>1.80096336911262</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>246938.593</t>
+          <t>1.87867561220575</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>253228.389</t>
+          <t>1.74341202729589</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>258805.731</t>
+          <t>1.82140619523593</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>263627.014</t>
+          <t>1.80750497838553</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>269026.187</t>
+          <t>1.57999397387567</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>266094.82</t>
+          <t>1.50167269702502</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>262808.915</t>
+          <t>1.46141765259821</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>261841.126</t>
+          <t>1.38267693247185</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>264757.46</t>
+          <t>1.40379921629876</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>267643.044</t>
+          <t>1.44433285068434</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>273342.068</t>
+          <t>1.50787302748126</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>275293.945</t>
+          <t>1.66181691371103</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>271688.068</t>
+          <t>1.92036096264978</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>259200.648</t>
+          <t>1.96005292800293</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>222377.918</t>
+          <t>266619568610.663</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>226311.857</t>
+          <t>268050378077.281</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>232419.816</t>
+          <t>271536469291.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>238264.033</t>
+          <t>275467417516.574</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>243345.874</t>
+          <t>284273666932.437</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>248180.096</t>
+          <t>300756130915.549</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>245372.044</t>
+          <t>286215327522.596</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>242440.736</t>
+          <t>275089511670.755</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>240823.365</t>
+          <t>279073679794.48</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>243449.993</t>
+          <t>294836583798.267</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>247601.002</t>
+          <t>304590662628.45</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>252739.809</t>
+          <t>311802275091.805</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>254926.998</t>
+          <t>301327725818.067</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>252853.572</t>
+          <t>298776669343.293</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>240900.197</t>
+          <t>250210136889.878</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>127117342051.982</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>126819461643.896</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>130495878469.801</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>140827921151.404</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>148007368996.208</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>166667123582.821</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>171727130493.177</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>174676566927.432</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>179798995052.287</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>185318580946.895</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>189054024606.396</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>187923467333.517</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>176109673439.396</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>164200049940.332</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>153642358680.157</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>1082385.25748597</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.03</t>
+          <t>1028097.53319523</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>988976.016862717</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>978400.061528258</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>984017.229336613</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>990996.668786415</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>953953.656470635</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56.35</t>
+          <t>933511.837191333</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>893921.265833423</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>870603.660058366</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>847376.348290287</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>814655.623078524</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>741933.769022522</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>702456.105945347</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>675951.251892918</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>729021.413603972</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>743525.354275919</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>756017.608964852</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>765198.308586843</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>805606.343523567</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>841029.734395578</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>803566.732659984</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>802876.51499024</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>856234.712816585</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>955981.047576001</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1033193.40901991</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1110555.91259791</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>1255070.96077175</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>1362741.57991153</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>1193133.01256049</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>2075477.16879347</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>2102229.26078075</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>2115898.24444565</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>2134900.09133817</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>2294470.95693763</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>2477783.55153935</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>2295992.27673124</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>2255892.35778039</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>2465366.0399651</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>2870529.83590764</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>3175960.9726989</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>3407584.38251061</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>3725123.60574935</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>4089457.73268862</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>3194631.24709005</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>0.749390870842535</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>64.89</t>
+          <t>0.784519934433816</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>0.781051005514336</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>0.691880635218429</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0.644147013744164</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>0.489076493389305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>0.428848450876868</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>0.387940808740614</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>0.339403285882754</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>0.313683667775286</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>62.98</t>
+          <t>0.309683845078383</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>0.344908184383151</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>0.447546818606871</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>0.539911664203745</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>62.67</t>
+          <t>0.567928264820756</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>1399827.26803539</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>1443082.12201214</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>1499854.86951382</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>1523889.99594355</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>1607511.00123559</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>1706741.1994334</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>1747700.9362169</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>1735706.62610792</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>1752771.61836829</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>1815309.71499575</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>1899793.23249477</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>1999850.73103332</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>2111579.01048659</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>2255094.07155205</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>2307970.69815729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0000000020846</t>
+          <t>1029.14210539822</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.999999998842423</t>
+          <t>1010.03439403803</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.999999995079282</t>
+          <t>1019.05167069432</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.99999999562278</t>
+          <t>1070.09838380252</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.999999996660455</t>
+          <t>1100.70082233908</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.00000000300325</t>
+          <t>1211.78738755253</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.9999999982869</t>
+          <t>1255.84676686519</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.999999996719295</t>
+          <t>1289.25830416276</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.999999999213553</t>
+          <t>1332.33252862525</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.00000000130348</t>
+          <t>1357.68576869299</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.000000002288</t>
+          <t>1358.67728835136</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.999999996442966</t>
+          <t>1328.40008793023</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.00000000279833</t>
+          <t>1232.93696335335</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.00000000415777</t>
+          <t>1153.76158405175</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.999999995453474</t>
+          <t>1128.27059471036</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>121623073469.064</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>122901243807.728</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>129301105530.559</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.908</t>
+          <t>135650380495.312</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.214</t>
+          <t>135890450263.492</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.636</t>
+          <t>146561442286.577</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.846</t>
+          <t>147456402673.077</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.991</t>
+          <t>147930779290.24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>153321963782.521</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.575</t>
+          <t>164316150609.873</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>6.954</t>
+          <t>167019541861.148</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.354</t>
+          <t>170578869547.089</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>7.764</t>
+          <t>162566482944.101</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>144675352957.061</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7.756</t>
+          <t>142744071658.409</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>102926608833.129</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.688</t>
+          <t>103674833904.762</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>110248072941.749</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5.309</t>
+          <t>117119646020.057</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.622</t>
+          <t>116761007782.59</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.081</t>
+          <t>126473960459.686</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.309</t>
+          <t>128379415380.986</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>129403039134.864</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6.766</t>
+          <t>135817202671.116</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7.112</t>
+          <t>145570547519.767</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7.476</t>
+          <t>147013729901.965</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.914</t>
+          <t>149793050343.047</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>8.333</t>
+          <t>139913373429.975</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>8.529</t>
+          <t>126457879293.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>125576530922.444</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18.821</t>
+          <t>18696464635.9357</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.468</t>
+          <t>19226409902.9652</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19053032588.8095</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20.583</t>
+          <t>18530734475.2549</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.128</t>
+          <t>19129442480.902</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22.081</t>
+          <t>20087481826.8906</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23.016</t>
+          <t>19076987292.0909</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23.567</t>
+          <t>18527740155.3761</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24.422</t>
+          <t>17504761111.4053</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26.072</t>
+          <t>18745603090.1059</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>27.759</t>
+          <t>20005811959.1835</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>28.717</t>
+          <t>20785819204.0426</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>28.562</t>
+          <t>22653109514.1261</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>29.835</t>
+          <t>18217473663.8105</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>29.951</t>
+          <t>17167540735.9645</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13.475</t>
+          <t>1800.37180398332</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14.273</t>
+          <t>1802.42651062464</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.168</t>
+          <t>1814.98300276117</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15.986</t>
+          <t>1810.47873333402</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17.016</t>
+          <t>1809.71397007455</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18.305</t>
+          <t>1804.44411379012</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18.576</t>
+          <t>1794.41470737405</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18.873</t>
+          <t>1789.41421335521</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19.828</t>
+          <t>1784.53056672914</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21.265</t>
+          <t>1783.56962030292</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>23.072</t>
+          <t>1779.43769522868</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>1786.57615039267</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25.795</t>
+          <t>1784.73397884496</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>26.565</t>
+          <t>1776.69092099148</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24.803</t>
+          <t>1769.04735581249</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7.421</t>
+          <t>1812.04152061456</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>1815.41892006397</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.336</t>
+          <t>1827.73258264738</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>8.791</t>
+          <t>1824.02174761821</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9.351</t>
+          <t>1823.97401194211</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>1821.23096137467</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>1812.41488810342</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10.641</t>
+          <t>1807.50107292978</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11.138</t>
+          <t>1803.44971393346</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11.866</t>
+          <t>1802.72674134739</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12.637</t>
+          <t>1797.42819255449</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13.396</t>
+          <t>1806.39153266805</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>1804.41168979112</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>1790.45123930817</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14.117</t>
+          <t>1783.34963846692</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>765225.323280749</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>816263.572723101</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>902571.294436322</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>864155.90461674</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>889289.080588457</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>982508.583328981</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>924669.562171277</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>903145.931181632</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>945047.328505496</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>1073132.50756792</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1187011.26399842</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>1348900.28791161</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>1530925.40769045</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1641838.63600932</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>1402113.67875685</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>23064825136.4546</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>102.71</t>
+          <t>23401807732.3483</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>105.3</t>
+          <t>24597556002.0569</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>22946309621.257</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>23049531036.9747</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>25866997570.2981</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70.04</t>
+          <t>23642771976.0518</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>21610879272.4352</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>21759665651.9557</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>24618991508.9042</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>25737974083.4421</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>28262485626.8954</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>29015387832.1045</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>31124604845.6761</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>94.39</t>
+          <t>24359176629.2404</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>180.1</t>
+          <t>836252.814511321</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>187.87</t>
+          <t>892267.221763333</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>174.34</t>
+          <t>969989.914351957</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>182.14</t>
+          <t>987743.852605666</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>180.75</t>
+          <t>1111816.71322843</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1316038.53269519</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150.17</t>
+          <t>1252718.02737742</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>146.14</t>
+          <t>1281712.50205058</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1391176.22539431</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>1624997.12064493</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>144.43</t>
+          <t>1834853.24155983</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>150.79</t>
+          <t>2032551.14878045</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>166.18</t>
+          <t>2161402.76732619</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>192.04</t>
+          <t>2337644.78531994</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>196.01</t>
+          <t>1779776.51207469</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>242776.093</t>
+          <t>155655801055.869</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>246938.593</t>
+          <t>157568821142.565</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>253228.389</t>
+          <t>163124948771.041</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>258805.731</t>
+          <t>176400094866.882</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>263627.014</t>
+          <t>191719178110.856</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>269026.187</t>
+          <t>221942126781.165</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>266094.82</t>
+          <t>222308803374.956</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>262808.915</t>
+          <t>227979138104.988</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>261841.126</t>
+          <t>240052211338.043</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>264757.46</t>
+          <t>262633950242.463</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>267643.044</t>
+          <t>272951369092.254</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>273342.068</t>
+          <t>276027778367.032</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>275293.945</t>
+          <t>254347046255.684</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>271688.068</t>
+          <t>237110347597.343</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>259200.648</t>
+          <t>203692560289.337</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>222377.918</t>
+          <t>-71027.4912305726</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>226311.857</t>
+          <t>-76003.6490402315</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>232419.816</t>
+          <t>-67418.619915635</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>238264.033</t>
+          <t>-123587.947988926</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>243345.874</t>
+          <t>-222527.632639969</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>248180.096</t>
+          <t>-333529.949366208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>245372.044</t>
+          <t>-328048.465206144</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>242440.736</t>
+          <t>-378566.570868951</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>240823.365</t>
+          <t>-446128.896888809</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>243449.993</t>
+          <t>-551864.613077001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>247601.002</t>
+          <t>-647841.977561411</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>252739.809</t>
+          <t>-683650.860868848</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>254926.998</t>
+          <t>-630477.359635741</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>252853.572</t>
+          <t>-695806.149310616</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>240900.197</t>
+          <t>-377662.833317842</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>266619.569</t>
+          <t>-132590975919.414</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>268050.378</t>
+          <t>-134167013410.217</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>271536.469</t>
+          <t>-138527392768.984</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>275467.418</t>
+          <t>-153453785245.625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>284273.667</t>
+          <t>-168669647073.881</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>300756.131</t>
+          <t>-196075129210.867</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>286215.328</t>
+          <t>-198666031398.905</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>275089.512</t>
+          <t>-206368258832.553</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>279073.68</t>
+          <t>-218292545686.087</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>294836.584</t>
+          <t>-238014958733.558</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>304590.663</t>
+          <t>-247213395008.812</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>311802.275</t>
+          <t>-247765292740.137</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>301327.726</t>
+          <t>-225331658423.58</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>298776.669</t>
+          <t>-205985742751.667</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>250210.137</t>
+          <t>-179333383660.097</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>2481581.52908</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2601500.87503</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2728773.84402</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.135</t>
+          <t>2860237.03224</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>3011908.57278</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>3153277.12626</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>3174749.14446</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>3247880.3611</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.465</t>
+          <t>3413364.94667</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.871</t>
+          <t>3709101.98696</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3927881.71778</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>4182870.69581</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>4362060.14796</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>4.089</t>
+          <t>4448510.34399</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>4247382.99525</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>93651.416</t>
+          <t>0.0827483145243228</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>94805.194</t>
+          <t>0.0880419732613603</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>97020.9</t>
+          <t>0.092657334365213</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>98733.989</t>
+          <t>0.0951668600958765</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>99810.664</t>
+          <t>0.100431300522277</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>102085.127</t>
+          <t>0.0979347699306751</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100171.555</t>
+          <t>0.0967603486554795</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>97904.897</t>
+          <t>0.103730692648302</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>96923.77</t>
+          <t>0.107222921458774</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>98190.3</t>
+          <t>0.112731366452803</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>99088.455</t>
+          <t>0.117467026742387</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>101618.572</t>
+          <t>0.121255685488929</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>101523.525</t>
+          <t>0.126571038915979</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>99562.196</t>
+          <t>0.120124084232105</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>93448.649</t>
+          <t>0.116841401590213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>4111271.34380874</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>4319358.82722058</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>4589681.86829822</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>4907901.94376541</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>5214254.20605125</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>5636194.04466866</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>5845754.13298404</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>5990808.40708692</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>6259694.94570284</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>6574879.48097678</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>6954263.47887655</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>7354289.12302536</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>7764091.97723864</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>7980292.02050788</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>7755767.15769361</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>127117.342</t>
+          <t>4464095.61405741</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>126819.462</t>
+          <t>4688432.49356206</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>130495.878</t>
+          <t>4974147.50682848</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>140827.921</t>
+          <t>5308510.72048344</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>148007.369</t>
+          <t>5622009.90984497</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>166667.124</t>
+          <t>6080751.6551146</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>171727.13</t>
+          <t>6309483.70364426</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>174676.567</t>
+          <t>6460328.12366782</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>179798.995</t>
+          <t>6766131.10358599</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>185318.581</t>
+          <t>7111650.34206001</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>189054.025</t>
+          <t>7475981.94805311</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>187923.467</t>
+          <t>7914364.89918369</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>176109.673</t>
+          <t>8333069.16370465</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>164200.05</t>
+          <t>8528874.97863706</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>153642.359</t>
+          <t>8309518.9298135</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>18820738.7267015</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>19467731.1849622</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>20100491.6054108</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>20582893.4693189</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>21128069.7648515</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>22081105.0672071</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>23016105.2719886</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>23566756.2963514</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>24422075.8107447</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>26071712.8527379</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>27759307.9911121</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>28717271.640767</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>28562155.6013977</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>29834682.0875331</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>56.79</t>
+          <t>29950773.6097914</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>4464095.61405741</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>4618134.06551089</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>4814977.98990195</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>5076899.34352241</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>5305516.48050572</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>5669643.35579082</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>5836610.34673127</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>5883198.84464637</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>6058920.49734251</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>6221164.41130242</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>6379285.68208567</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>6623323.4142658</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>6818904.07859186</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>6860087.69765911</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>6504620.82767745</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4111271.34380874</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4256259.01263842</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4445784.69312123</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4699256.47206462</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4929195.97370424</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5268368.89972042</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5428023.58509812</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5472332.77054786</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5625015.66957408</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5782075.40858483</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5958112.24035796</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6182964.88929049</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6382953.28214258</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6440763.98475052</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6087617.53329479</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2957211.67577259</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3157059.59045794</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3362312.84110152</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3482699.33910656</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3729430.52524503</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3869249.1440054</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3974747.30702574</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4180302.58020218</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4371377.93488401</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4754409.53064999</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5160596.60663689</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5481983.18920631</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>5726720.71863535</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>5838957.93567294</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5807461.0654365</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>222377917711.506</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>226311857377.698</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>232419815564.116</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>238264032694.127</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>243345873747.246</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>248180095947.989</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>245372044378.705</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>242440735569.293</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>240823364771.45</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>243449993125.228</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>247601001874.047</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>252739809254.507</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>254926997513.093</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>252853572165.955</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>240900196848.347</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>242776092779.119</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>246938593291.553</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>253228388684.215</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>258805730809.544</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>263627013743.852</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>269026187370.179</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>266094819734.222</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>262808915243.401</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>261841125587.143</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>264757460055.455</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>267643044069.724</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>273342067665.799</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>275293944514.337</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>271688067727.256</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>259200647761.736</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>93651415551.8366</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>94805193725.4861</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>97020900130.2675</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>98733988915.7743</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>99810663841.7137</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>102085127147.043</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100171554541.105</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>97904896782.3505</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>96923770425.9432</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>98190300172.9559</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>99088454732.8965</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>101618572365.201</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>101523524686.793</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>99562195536.8395</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>93448649096.0491</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>133979321.123271</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>136022925.92767</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>138547833.030053</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141887415.074678</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>144534413.329251</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>147716677.936947</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>146817829.339657</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>145399036.924174</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>145189036.081327</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>146864998.439847</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>148903330.424206</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>151319391.572917</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>152567147.548354</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>151742790.734829</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>145344828.726105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>123517774.061721</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>125559547.667366</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>128056194.03076</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>131602779.036991</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>134466483.527903</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>137538255.716162</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>136742105.02754</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>135486090.229891</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>134950540.641539</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>136495929.485433</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>139145642.771284</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>141466015.427866</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>142837532.391284</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>142317140.915456</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>136175097.889172</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>242776092779.119</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>246938593291.553</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>253228388684.215</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>258805730809.544</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>263627013743.852</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>269026187370.179</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>266094819734.222</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>262808915243.401</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>261841125587.143</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>264757460055.455</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>267643044069.724</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>273342067665.799</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>275293944514.337</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>271688067727.256</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>259200647761.736</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>222377917711.506</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>226311857377.698</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>232419815564.116</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>238264032694.127</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>243345873747.246</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>248180095947.989</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>245372044378.705</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>242440735569.293</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>240823364771.45</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>243449993125.228</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>247601001874.047</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>252739809254.507</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>254926997513.093</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>252853572165.955</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>240900196848.347</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.316193820598937</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.315040474579303</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.314148865416901</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.324167870372589</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.325728184531695</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.338735173747623</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.347724687054552</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.349000421584222</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.340986203952517</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.359613721853134</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.361083830034479</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.369212977323187</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.364127458318386</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.375007521109898</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.379223506756898</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.584390359486787</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.590349649645511</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.582830657193358</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.583688997296989</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.582617935738407</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.573386304427815</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.566839573924319</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.563500494379218</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.567575384021138</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.557947784553062</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.557538159938588</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.549410554976046</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.558717571172456</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.55023438139401</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.549429508172603</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0994158199142756</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0946098757751858</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.103020477389742</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0921431323304222</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0916538797298983</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0878785218245616</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0854357390211285</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0874990840365595</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0914384120263447</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.082438493593804</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0813780100269325</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0813764677007675</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0771549705091588</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0747580974960919</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0713469850704996</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.218959302225379</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.219126429312119</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.220748431530531</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.226290023236293</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.227049318701311</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.229904784708502</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.234548729053835</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.235991254564596</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.23231094231555</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.244305192036868</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.24660362088919</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.250359099446739</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.251805968717819</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.255890685345024</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.26432732549474</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.644182234776234</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.648892437876221</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.641396686981481</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.644486321916615</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.639986161568194</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.642458079769947</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.638582952099535</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.631547031092499</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.631359293288519</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.629551079491841</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.629840257277529</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.625214446030152</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.630852286123446</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.629026818574473</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.62670060370545</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.136858462998387</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.13198113281166</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.137854881487988</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.129223654847093</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.132964519730495</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.127637135521551</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.12686831884663</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.132461714342905</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.13632976439593</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.126143728471291</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.123556121833281</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.124426454523109</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.117341745158735</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.115082496080503</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.10897207079981</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13475212.97756</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14272864.33987</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>15168254.22658</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>15986187.04982</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17016289.90821</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>18304783.0254</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>18575525.02881</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18873334.93361</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>19828498.0708</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>21264711.10108</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23072266.03663</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>24479922.10987</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>25795266.07911</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>26565031.96168</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>24802899.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7421307.28983</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7845492.08402</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8336460.34793</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8791210.05959</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9351440.43509</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9950000.79912</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10284231.01067</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10640630.70387</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11137509.03847</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>11866059.87271</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12636578.55469</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>13396348.08839</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>14059789.88234</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>14367832.91431</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>14116979.99525</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>18820738.9191827</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19498613.6525624</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20283897.9383015</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>21189899.9145217</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22263534.1456492</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>23387726.465827</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>24337515.189576</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>25106423.4745591</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>25927327.1323067</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>26827138.3114804</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>27863993.3167719</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>29027701.0853574</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>30191130.2566561</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>31033568.8035416</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>31372991.962419</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
